--- a/Datasetsd.xlsx
+++ b/Datasetsd.xlsx
@@ -1,26 +1,73 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\limad\OneDrive\Documentos\GitHub\trabalhoMLmsc\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3129827-F354-4FB1-913F-3B526711EAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="8">
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Good</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Dataset02</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Dataset03</t>
+  </si>
+  <si>
+    <t>Dataset01 - Mendeley</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +75,47 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9D9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +123,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -66,6 +177,4291 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Distruibuição</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> de dados Dataset 01</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$2:$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset01 - Mendeley</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>400</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EC9A-4078-97AB-5EB7B1EAA764}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$2:$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset01 - Mendeley</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Test</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EC9A-4078-97AB-5EB7B1EAA764}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1083820896"/>
+        <c:axId val="1083821376"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1083820896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1083821376"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1083821376"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1083820896"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Distruibuição de dados Dataset 02</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$7:$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$9:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$9:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>144.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>134.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-86B4-4EF4-8B9B-9D16DD2ADB2A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$7:$C$8</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset02</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Test</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$9:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$9:$C$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>36.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>33.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-86B4-4EF4-8B9B-9D16DD2ADB2A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1823095471"/>
+        <c:axId val="1413165727"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1823095471"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1413165727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1413165727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1823095471"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Distruibuição de dados Dataset 03</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$12:$B$13</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset03</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Train</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$14:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$14:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>544.80000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>534.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9F9C-4C3D-A36A-BFB3A90C8F93}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$12:$C$13</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Dataset03</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Test</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="ctr"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$14:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>Bad</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Good</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$14:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="2"/>
+                <c:pt idx="0">
+                  <c:v>136.20000000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>133.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9F9C-4C3D-A36A-BFB3A90C8F93}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="ctr"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="1755766943"/>
+        <c:axId val="1403389983"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1755766943"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1403389983"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1403389983"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1755766943"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Comparação entre os</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR" baseline="0"/>
+              <a:t> datasets</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:multiLvlStrRef>
+              <c:f>Sheet2!$F$4:$G$11</c:f>
+              <c:multiLvlStrCache>
+                <c:ptCount val="8"/>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Bad</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Good</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Bad</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Good</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Bad</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Good</c:v>
+                  </c:pt>
+                </c:lvl>
+                <c:lvl>
+                  <c:pt idx="0">
+                    <c:v>Dataset01 - Mendeley</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>Dataset02</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Dataset03</c:v>
+                  </c:pt>
+                </c:lvl>
+              </c:multiLvlStrCache>
+            </c:multiLvlStrRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$H$4:$H$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>681</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>668</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8261-458F-9D86-111041C4DFE9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="1413164767"/>
+        <c:axId val="1245807616"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1413164767"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1245807616"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1245807616"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1413164767"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="297">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>257175</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>561975</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B94B3E5F-28D8-0454-8D94-2A28D483522D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>158461</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>3175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>463261</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>168274</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Chart 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA717929-37D1-3EDF-9B8C-AB61E01FF040}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>196272</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>2310</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>484909</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>159328</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC777F2C-D5A8-AF1B-ACAF-A9F326FC24C1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>34925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>15875</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BB1D78E-DCD7-9A7C-68ED-580636D79051}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +4726,294 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:D15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4">
+        <f>$D$4*80%</f>
+        <v>400</v>
+      </c>
+      <c r="C4">
+        <f>$D$4*20%</f>
+        <v>100</v>
+      </c>
+      <c r="D4" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <f>$D$5*80%</f>
+        <v>400</v>
+      </c>
+      <c r="C5">
+        <f>$D$5*20%</f>
+        <v>100</v>
+      </c>
+      <c r="D5" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9">
+        <f>$D$9*80%</f>
+        <v>144.80000000000001</v>
+      </c>
+      <c r="C9">
+        <f>$D$9*20%</f>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="D9" s="1">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <f>$D$10*80%</f>
+        <v>134.4</v>
+      </c>
+      <c r="C10">
+        <f>$D$10*20%</f>
+        <v>33.6</v>
+      </c>
+      <c r="D10" s="1">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14">
+        <f>D14*80%</f>
+        <v>544.80000000000007</v>
+      </c>
+      <c r="C14">
+        <f>D14*20%</f>
+        <v>136.20000000000002</v>
+      </c>
+      <c r="D14" s="1">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15">
+        <f>D15*80%</f>
+        <v>534.4</v>
+      </c>
+      <c r="C15">
+        <f>D15*20%</f>
+        <v>133.6</v>
+      </c>
+      <c r="D15" s="1">
+        <v>668</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E089548D-3CBC-409F-AB71-C6769111971C}">
+  <dimension ref="A3:H12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3"/>
+    </row>
+    <row r="4" spans="1:8" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1">
+        <v>500</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>500</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1">
+        <v>181</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="1">
+        <v>168</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="5">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="1">
+        <v>681</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H10" s="5">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1">
+        <v>668</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="5">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B12" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Datasetsd.xlsx
+++ b/Datasetsd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\limad\OneDrive\Documentos\GitHub\trabalhoMLmsc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8845de8732abbeb5/Documentos/GitHub/trabalhoMLmsc/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3129827-F354-4FB1-913F-3B526711EAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5320" yWindow="3120" windowWidth="14310" windowHeight="7300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -151,7 +151,6 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4889,10 +4888,9 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3"/>
     </row>
     <row r="4" spans="1:8" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
@@ -4901,13 +4899,13 @@
       <c r="B4" s="1">
         <v>500</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>500</v>
       </c>
     </row>
@@ -4918,11 +4916,11 @@
       <c r="B5" s="1">
         <v>500</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="5"/>
+      <c r="G5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>500</v>
       </c>
     </row>
@@ -4931,9 +4929,9 @@
         <v>4</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
@@ -4942,13 +4940,13 @@
       <c r="B7" s="1">
         <v>181</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
         <v>181</v>
       </c>
     </row>
@@ -4959,11 +4957,11 @@
       <c r="B8" s="1">
         <v>168</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5"/>
+      <c r="G8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="4">
         <v>168</v>
       </c>
     </row>
@@ -4972,9 +4970,9 @@
         <v>6</v>
       </c>
       <c r="B9" s="2"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
@@ -4983,13 +4981,13 @@
       <c r="B10" s="1">
         <v>681</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="4">
         <v>681</v>
       </c>
     </row>
@@ -5000,11 +4998,11 @@
       <c r="B11" s="1">
         <v>668</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="5"/>
+      <c r="G11" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="4">
         <v>668</v>
       </c>
     </row>

--- a/Datasetsd.xlsx
+++ b/Datasetsd.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8845de8732abbeb5/Documentos/GitHub/trabalhoMLmsc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3129827-F354-4FB1-913F-3B526711EAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{E3129827-F354-4FB1-913F-3B526711EAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A25E0AC-1BB7-40D0-AE5C-96873E5B7CFA}"/>
   <bookViews>
-    <workbookView xWindow="5320" yWindow="3120" windowWidth="14310" windowHeight="7300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="35055" yWindow="5340" windowWidth="14235" windowHeight="7275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +160,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -882,7 +883,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$9:$B$10</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>144.80000000000001</c:v>
@@ -1002,7 +1003,7 @@
             <c:numRef>
               <c:f>Sheet1!$C$9:$C$10</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>36.200000000000003</c:v>
@@ -1105,7 +1106,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1400,7 +1401,7 @@
             <c:numRef>
               <c:f>Sheet1!$B$14:$B$15</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>544.80000000000007</c:v>
@@ -1520,7 +1521,7 @@
             <c:numRef>
               <c:f>Sheet1!$C$14:$C$15</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>136.20000000000002</c:v>
@@ -1623,7 +1624,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4799,11 +4800,11 @@
       <c r="A9" t="s">
         <v>0</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="6">
         <f>$D$9*80%</f>
         <v>144.80000000000001</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="6">
         <f>$D$9*20%</f>
         <v>36.200000000000003</v>
       </c>
@@ -4815,11 +4816,11 @@
       <c r="A10" t="s">
         <v>1</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="6">
         <f>$D$10*80%</f>
         <v>134.4</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <f>$D$10*20%</f>
         <v>33.6</v>
       </c>
@@ -4845,11 +4846,11 @@
       <c r="A14" t="s">
         <v>0</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="6">
         <f>D14*80%</f>
         <v>544.80000000000007</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="6">
         <f>D14*20%</f>
         <v>136.20000000000002</v>
       </c>
@@ -4861,11 +4862,11 @@
       <c r="A15" t="s">
         <v>1</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="6">
         <f>D15*80%</f>
         <v>534.4</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="6">
         <f>D15*20%</f>
         <v>133.6</v>
       </c>
